--- a/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/08_BIBS_UXScreens_BRD-01_New_Business_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-01_New_Business/08_BIBS_UXScreens_BRD-01_New_Business_v2.0.xlsx
@@ -1158,7 +1158,7 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Version 2.0, 27 September 2026</t>
+          <t>Version 2.0, 1 October 2026</t>
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
